--- a/TEngine/Configs/GameConfig/Datas/item.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D319DCE-5BD7-4C6B-9ACE-59C6FCC1048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B38A99E-FAB0-4C37-8CA9-2EF4C67B6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,14 @@
   </si>
   <si>
     <t>Common_GoldCoin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示道具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_Light</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -682,6 +690,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>10001</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEngine/Configs/GameConfig/Datas/item.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B38A99E-FAB0-4C37-8CA9-2EF4C67B6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517BD38B-2805-4FFB-B913-B017A44E4378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,15 +107,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Common_GoldCoin</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>提示道具</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Common_Light</t>
+    <t>Common_coin_icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_hint_button</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +687,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
@@ -695,7 +695,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>

--- a/TEngine/Configs/GameConfig/Datas/item.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517BD38B-2805-4FFB-B913-B017A44E4378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADB5C68-4E17-404F-BFC4-EAE82E120B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -45,6 +46,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -75,6 +77,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -85,6 +88,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -116,6 +120,14 @@
   </si>
   <si>
     <t>Common_hint_button</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重置道具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_reset_button</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -135,6 +147,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -142,6 +155,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -507,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -701,6 +715,17 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>10002</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
